--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Desktop\Documents\Mani\Apps\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60193067-E8D0-4001-AA3A-CB756CA39CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A1FE96DC-6E05-46D9-AE55-1140B796CF97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8AEC3938-9122-4AD1-8C1B-AEB0B8A39961}"/>
   </bookViews>
@@ -557,7 +557,7 @@
         <v>29</v>
       </c>
       <c r="F2">
-        <v>58000</v>
+        <v>60000</v>
       </c>
       <c r="G2">
         <v>4</v>
@@ -768,7 +768,7 @@
         <v>73000</v>
       </c>
       <c r="G10">
-        <v>6</v>
+        <v>60</v>
       </c>
       <c r="H10">
         <v>4.3</v>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Desktop\Documents\Mani\Apps\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{60193067-E8D0-4001-AA3A-CB756CA39CAA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD42922C-76FE-48F9-ACE8-4B22F1A40961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8AEC3938-9122-4AD1-8C1B-AEB0B8A39961}"/>
   </bookViews>
@@ -102,9 +102,6 @@
     <t>Operations</t>
   </si>
   <si>
-    <t>Denver</t>
-  </si>
-  <si>
     <t>Grace Taylor</t>
   </si>
   <si>
@@ -157,6 +154,9 @@
   </si>
   <si>
     <t>San Diego</t>
+  </si>
+  <si>
+    <t>Denver1</t>
   </si>
 </sst>
 </file>
@@ -563,7 +563,7 @@
         <v>4</v>
       </c>
       <c r="H2">
-        <v>4.5</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.25">
@@ -681,7 +681,7 @@
         <v>24</v>
       </c>
       <c r="D7" t="s">
-        <v>25</v>
+        <v>43</v>
       </c>
       <c r="E7">
         <v>45</v>
@@ -701,13 +701,13 @@
         <v>1007</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="C8" t="s">
         <v>9</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E8">
         <v>26</v>
@@ -727,13 +727,13 @@
         <v>1008</v>
       </c>
       <c r="B9" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
         <v>15</v>
       </c>
       <c r="D9" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E9">
         <v>38</v>
@@ -753,13 +753,13 @@
         <v>1009</v>
       </c>
       <c r="B10" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="C10" t="s">
         <v>12</v>
       </c>
       <c r="D10" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E10">
         <v>30</v>
@@ -779,13 +779,13 @@
         <v>1010</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="C11" t="s">
         <v>21</v>
       </c>
       <c r="D11" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E11">
         <v>35</v>
@@ -805,13 +805,13 @@
         <v>1011</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="C12" t="s">
         <v>18</v>
       </c>
       <c r="D12" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E12">
         <v>33</v>
@@ -831,13 +831,13 @@
         <v>1012</v>
       </c>
       <c r="B13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C13" t="s">
         <v>24</v>
       </c>
       <c r="D13" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E13">
         <v>28</v>
@@ -857,13 +857,13 @@
         <v>1013</v>
       </c>
       <c r="B14" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C14" t="s">
         <v>9</v>
       </c>
       <c r="D14" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E14">
         <v>25</v>
@@ -883,13 +883,13 @@
         <v>1014</v>
       </c>
       <c r="B15" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C15" t="s">
         <v>15</v>
       </c>
       <c r="D15" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E15">
         <v>42</v>
@@ -909,13 +909,13 @@
         <v>1015</v>
       </c>
       <c r="B16" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C16" t="s">
         <v>21</v>
       </c>
       <c r="D16" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E16">
         <v>36</v>
@@ -927,7 +927,7 @@
         <v>11</v>
       </c>
       <c r="H16">
-        <v>4.9000000000000004</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/Book1.xlsx
+++ b/Book1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Desktop\Documents\Mani\Apps\excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD42922C-76FE-48F9-ACE8-4B22F1A40961}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB2741F6-C369-419C-BB9E-E88BB29F5CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{8AEC3938-9122-4AD1-8C1B-AEB0B8A39961}"/>
   </bookViews>
@@ -635,7 +635,7 @@
         <v>27</v>
       </c>
       <c r="F5">
-        <v>52000</v>
+        <v>52001</v>
       </c>
       <c r="G5">
         <v>3</v>
